--- a/PPP_empirical_reinforcement_bundle_20260416_unified_v3/04_manuscript_integration/tables/robustness_defense_summary.xlsx
+++ b/PPP_empirical_reinforcement_bundle_20260416_unified_v3/04_manuscript_integration/tables/robustness_defense_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-0.1699354582537249</v>
+        <v>-0.1699354582534498</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4092905410846794</v>
+        <v>0.4092905410846416</v>
       </c>
       <c r="I2" t="n">
-        <v>0.677999029924208</v>
+        <v>0.6779990299246719</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.9610150694203422</v>
+        <v>0.9610150694204008</v>
       </c>
       <c r="O2" t="n">
         <v>0.2372372372372372</v>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.2262861101927882</v>
+        <v>0.2262861101927911</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1744093771933589</v>
+        <v>0.1744093771934292</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1944790328877616</v>
+        <v>0.1944790328879358</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.08879746543807482</v>
+        <v>0.08879746543806405</v>
       </c>
       <c r="O3" t="n">
         <v>0.07607607607607608</v>
@@ -684,13 +684,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-0.35210675967008</v>
+        <v>-0.3521067596700481</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1784378679689557</v>
+        <v>0.1784378679690451</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04846438271309223</v>
+        <v>0.04846438271322518</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.1698991651596306</v>
+        <v>0.1698991651596203</v>
       </c>
       <c r="O4" t="n">
         <v>0.1221221221221221</v>
